--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/5287-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/5287-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7599C212-57F4-4CD9-B1C6-A4B6D58AD6A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B42736DF-86DC-4FDD-80AF-02FC5CB8DAD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{37926143-CCEA-462C-930F-25F484EF82BA}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{1AF09071-5596-4651-AE26-396303347624}"/>
   </bookViews>
   <sheets>
     <sheet name="5287-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1562,26 +1562,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCFE327A-9A26-476D-BC5F-543318712C7D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4299187B-D5F5-487E-82FE-38D96670CAF4}">
   <dimension ref="A1:X31"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="8.125" customWidth="1"/>
-    <col min="24" max="24" width="8" customWidth="1"/>
+    <col min="1" max="1" width="3.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -1615,7 +1615,7 @@
       <c r="W1" s="34"/>
       <c r="X1" s="26"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="27" t="s">
         <v>1</v>
       </c>
@@ -1651,7 +1651,7 @@
       <c r="W2" s="36"/>
       <c r="X2" s="37"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="27" t="s">
         <v>2</v>
       </c>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="X3" s="40"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="29"/>
       <c r="B4" s="30"/>
       <c r="C4" s="7"/>
@@ -1771,7 +1771,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="41">
         <v>2025</v>
       </c>
@@ -1843,7 +1843,7 @@
         <v>3.03</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1917,7 +1917,7 @@
         <v>3.03</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="43">
         <v>2024</v>
       </c>
@@ -1989,7 +1989,7 @@
         <v>6.06</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>3.21</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2137,7 +2137,7 @@
         <v>2.84</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="41">
         <v>2023</v>
       </c>
@@ -2209,7 +2209,7 @@
         <v>5.79</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="45" t="s">
         <v>29</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>2.83</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="46"/>
       <c r="B12" s="46"/>
       <c r="C12" s="20" t="s">
@@ -2311,7 +2311,7 @@
       <c r="W12" s="52"/>
       <c r="X12" s="48"/>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -2385,7 +2385,7 @@
         <v>2.96</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="43">
         <v>2022</v>
       </c>
@@ -2457,7 +2457,7 @@
         <v>5.45</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="53" t="s">
         <v>29</v>
       </c>
@@ -2531,7 +2531,7 @@
         <v>2.91</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="54"/>
       <c r="B16" s="54"/>
       <c r="C16" s="23" t="s">
@@ -2559,7 +2559,7 @@
       <c r="W16" s="60"/>
       <c r="X16" s="56"/>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>29</v>
       </c>
@@ -2633,7 +2633,7 @@
         <v>2.54</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="41">
         <v>2021</v>
       </c>
@@ -2705,7 +2705,7 @@
         <v>6.38</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="61">
         <v>2020</v>
       </c>
@@ -2777,7 +2777,7 @@
         <v>6.71</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="63"/>
       <c r="B20" s="64"/>
       <c r="C20" s="24" t="s">
@@ -2805,7 +2805,7 @@
       <c r="W20" s="60"/>
       <c r="X20" s="56"/>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="41">
         <v>2019</v>
       </c>
@@ -2877,7 +2877,7 @@
         <v>7.44</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="43">
         <v>2018</v>
       </c>
@@ -2949,7 +2949,7 @@
         <v>5.22</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="41">
         <v>2017</v>
       </c>
@@ -3021,7 +3021,7 @@
         <v>7.31</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="43">
         <v>2016</v>
       </c>
@@ -3093,7 +3093,7 @@
         <v>8.02</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="41">
         <v>2015</v>
       </c>
@@ -3165,7 +3165,7 @@
         <v>7.47</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="43">
         <v>2014</v>
       </c>
@@ -3237,7 +3237,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="41">
         <v>2013</v>
       </c>
@@ -3309,7 +3309,7 @@
         <v>2.83</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="43">
         <v>2012</v>
       </c>
@@ -3381,7 +3381,7 @@
         <v>4.08</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="41">
         <v>2011</v>
       </c>
@@ -3453,7 +3453,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="43">
         <v>2010</v>
       </c>
@@ -3525,7 +3525,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="41" t="s">
         <v>49</v>
       </c>
